--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="503">
   <si>
     <t>Property</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Highest hyperglycemia value observation profile.</t>
+    <t>Observation profile for the highest recorded hyperglycemia value in the relevant stroke care interval.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -741,7 +741,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>registered | preliminary | final | amended +</t>
+    <t>Final registry observation</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -818,7 +818,7 @@
 </t>
   </si>
   <si>
-    <t>Type of observation (code / type)</t>
+    <t>Registry observation concept</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -862,10 +862,10 @@
 </t>
   </si>
   <si>
-    <t>Who and/or what the observation is about</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, device, organization, procedure or practitioner this observation is about and into whose or what record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>RES-Q registry patient</t>
+  </si>
+  <si>
+    <t>Patient who experienced the index stroke episode represented in this registry dataset.</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated. The subject of an Observation may in some cases be a procedure.  This supports the regulatory inspection use case where observations are captured during inspections of a procedure that is being performed (independent of any particular patient or whether patient related at all).</t>
@@ -916,10 +916,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+    <t>Index stroke encounter</t>
+  </si>
+  <si>
+    <t>Encounter that anchors the clinical fact to the acute stroke episode and hospital pathway.</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
@@ -1035,7 +1035,7 @@
 </t>
   </si>
   <si>
-    <t>Actual result</t>
+    <t>Highest glucose value</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1820,98 +1820,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2105,10 +2107,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2190,7 +2192,7 @@
         <v>82</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>80</v>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="503">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -830,10 +830,22 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://tecnomod-um.org/ValueSet/analitics-codes-vs</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://tecnomod-um.org/CodeSystem/analytics-codes-cs"/&gt;
+    &lt;code value="highest-hyperglycemia-value"/&gt;
+    &lt;display value="Highest Hyperglycemia Value"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|5.0.0</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1087,6 +1099,9 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
@@ -1172,9 +1187,6 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>SNOMED CT Body site concepts</t>
@@ -1553,12 +1565,6 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|5.0.0</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2956,7 +2962,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>81</v>
@@ -3074,7 +3080,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>94</v>
@@ -4907,7 +4913,7 @@
         <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>82</v>
@@ -4922,11 +4928,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4953,36 +4961,36 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>215</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5005,19 +5013,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5066,7 +5074,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5081,19 +5089,19 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5101,10 +5109,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5127,16 +5135,16 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5186,7 +5194,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5204,16 +5212,16 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5221,14 +5229,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5247,19 +5255,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5308,7 +5316,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5323,19 +5331,19 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5343,14 +5351,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5369,19 +5377,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5430,7 +5438,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5445,19 +5453,19 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5465,10 +5473,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5491,16 +5499,16 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5550,7 +5558,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5568,16 +5576,16 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5585,10 +5593,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5611,17 +5619,17 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5670,7 +5678,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5685,19 +5693,19 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5705,10 +5713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5731,19 +5739,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5792,7 +5800,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5801,7 +5809,7 @@
         <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>106</v>
@@ -5813,24 +5821,24 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5856,16 +5864,16 @@
         <v>243</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5890,13 +5898,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5914,7 +5922,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5923,7 +5931,7 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>106</v>
@@ -5941,7 +5949,7 @@
         <v>139</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -5949,14 +5957,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5978,16 +5986,16 @@
         <v>243</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6012,13 +6020,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6036,7 +6044,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6057,24 +6065,24 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6097,19 +6105,19 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6158,7 +6166,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6182,10 +6190,10 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6193,10 +6201,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6222,13 +6230,13 @@
         <v>243</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6254,13 +6262,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>366</v>
+        <v>260</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6278,7 +6286,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6287,7 +6295,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6299,24 +6307,24 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6339,16 +6347,16 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6398,7 +6406,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6407,7 +6415,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6425,7 +6433,7 @@
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6433,10 +6441,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6462,16 +6470,16 @@
         <v>243</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6496,13 +6504,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>366</v>
+        <v>260</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6520,7 +6528,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6544,10 +6552,10 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6555,10 +6563,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6581,16 +6589,16 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6640,7 +6648,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6652,7 +6660,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6661,24 +6669,24 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6701,16 +6709,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6760,7 +6768,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6781,24 +6789,24 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6824,16 +6832,16 @@
         <v>186</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6882,7 +6890,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6894,7 +6902,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6906,10 +6914,10 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6917,10 +6925,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7035,10 +7043,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7155,10 +7163,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7277,10 +7285,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7303,13 +7311,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7360,7 +7368,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7369,7 +7377,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7384,10 +7392,10 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7395,10 +7403,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7421,13 +7429,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7478,7 +7486,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7487,7 +7495,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7502,10 +7510,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7513,10 +7521,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7542,10 +7550,10 @@
         <v>243</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7572,13 +7580,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7596,7 +7604,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7620,10 +7628,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7631,10 +7639,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7660,16 +7668,16 @@
         <v>243</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7697,10 +7705,10 @@
         <v>248</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7718,7 +7726,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7739,13 +7747,13 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7753,10 +7761,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7782,16 +7790,16 @@
         <v>243</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7816,13 +7824,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>366</v>
+        <v>260</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7840,7 +7848,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7861,13 +7869,13 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7875,10 +7883,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7901,17 +7909,17 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7960,7 +7968,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7987,7 +7995,7 @@
         <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -7995,10 +8003,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8021,13 +8029,13 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8078,7 +8086,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8087,7 +8095,7 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -8102,10 +8110,10 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8113,10 +8121,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8139,16 +8147,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8198,7 +8206,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8222,7 +8230,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>209</v>
@@ -8233,10 +8241,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8259,16 +8267,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8318,7 +8326,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8342,10 +8350,10 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8353,10 +8361,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8382,16 +8390,16 @@
         <v>186</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8440,7 +8448,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8449,7 +8457,7 @@
         <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -8464,10 +8472,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8475,10 +8483,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8593,10 +8601,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8713,10 +8721,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8835,10 +8843,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8864,13 +8872,13 @@
         <v>243</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>258</v>
@@ -8898,13 +8906,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>366</v>
+        <v>260</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>487</v>
+        <v>261</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>488</v>
+        <v>262</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -8922,7 +8930,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>94</v>
@@ -8931,7 +8939,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -8940,13 +8948,13 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>489</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>215</v>
@@ -8989,13 +8997,13 @@
         <v>492</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>493</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9068,13 +9076,13 @@
         <v>494</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9117,7 +9125,7 @@
         <v>498</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9142,13 +9150,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9193,7 +9201,7 @@
         <v>139</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9208,7 +9216,7 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9230,16 +9238,16 @@
         <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9264,13 +9272,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9309,16 +9317,16 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="62" hidden="true">
@@ -9358,10 +9366,10 @@
         <v>502</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9434,10 +9442,10 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/highest-hyperglycemia-value-observation-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/highest-hyperglycemia-value-observation-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/base-stroke-observation</t>
+    <t>http://qualityregistry.org/StructureDefinition/base-stroke-observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -485,7 +485,7 @@
     <t>observationTimingContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/observation-timing-context-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/observation-timing-context-ext}
 </t>
   </si>
   <si>
@@ -832,7 +832,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://tecnomod-um.org/CodeSystem/analytics-codes-cs"/&gt;
+    &lt;system value="http://qualityregistry.org/CodeSystem/analytics-codes-cs"/&gt;
     &lt;code value="highest-hyperglycemia-value"/&gt;
     &lt;display value="Highest Hyperglycemia Value"/&gt;
   &lt;/coding&gt;
@@ -870,7 +870,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-patient-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-patient-profile)
 </t>
   </si>
   <si>
@@ -924,7 +924,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/stroke-encounter-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-encounter-profile)
 </t>
   </si>
   <si>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
+++ b/StructureDefinition-highest-hyperglycemia-value-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
